--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484365_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484365_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.941</v>
+        <v>4.9321</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2395</v>
+        <v>3.9856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7014</v>
+        <v>0.9466</v>
       </c>
       <c r="G2" t="n">
         <v>1.7715</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4829</v>
+        <v>1.474</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2398</v>
+        <v>0.9858</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2431</v>
+        <v>0.4883</v>
       </c>
       <c r="V2" t="n">
         <v>0.7098</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4636</v>
+        <v>3.1253</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2699</v>
+        <v>3.7954</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8063</v>
+        <v>-0.6702</v>
       </c>
       <c r="G3" t="n">
         <v>-0.08740000000000001</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3137</v>
+        <v>0.9754</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0964</v>
+        <v>0.6219</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2173</v>
+        <v>0.3534</v>
       </c>
       <c r="V3" t="n">
         <v>1.6512</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4497</v>
+        <v>2.4363</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6764</v>
+        <v>3.6358</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2267</v>
+        <v>-1.1995</v>
       </c>
       <c r="G4" t="n">
         <v>1.111</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.12</v>
+        <v>0.1066</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1707</v>
+        <v>0.1301</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0507</v>
+        <v>-0.0235</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0914</v>
+        <v>2.0274</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1882</v>
+        <v>1.1786</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9033</v>
+        <v>0.8488</v>
       </c>
       <c r="G5" t="n">
         <v>-1.694</v>
@@ -844,13 +844,13 @@
         <v>2.7348</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7104</v>
+        <v>0.2256</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.927</v>
+        <v>0.0634</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2166</v>
+        <v>0.1622</v>
       </c>
       <c r="V5" t="n">
         <v>2.7145</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4612</v>
+        <v>0.2921</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0401</v>
+        <v>0.0484</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5013</v>
+        <v>0.2437</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.384</v>
+        <v>-0.9029</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5188</v>
+        <v>-0.3768</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1348</v>
+        <v>-0.5261</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6536</v>
+        <v>1.4145</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6536</v>
+        <v>0.8608</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5537</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2696</v>
+        <v>-2.3174</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1348</v>
+        <v>-1.2377</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>-1.0797</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6499</v>
+        <v>0.7429</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6136</v>
+        <v>0.3454</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0363</v>
+        <v>0.3975</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4288</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.2102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2838</v>
+        <v>0.1112</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1015</v>
+        <v>-0.4445</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1823</v>
+        <v>0.5558</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6952</v>
+        <v>-0.384</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2763</v>
+        <v>-0.5188</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4189</v>
+        <v>0.1348</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5312</v>
+        <v>-0.6536</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6526</v>
+        <v>-0.6536</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1639</v>
+        <v>0.2696</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6237</v>
+        <v>0.1348</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5403</v>
+        <v>0.1348</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5601</v>
+        <v>0.2999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6687</v>
+        <v>0.2091</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1085</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5657</v>
+        <v>-0.4939</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6188</v>
+        <v>-0.2026</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0531</v>
+        <v>-0.2912</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9029</v>
+        <v>-2.6952</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3768</v>
+        <v>-2.2763</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5261</v>
+        <v>-0.4189</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4145</v>
+        <v>-1.5312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8608</v>
+        <v>-1.6526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5537</v>
+        <v>0.1214</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3174</v>
+        <v>-1.1639</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2377</v>
+        <v>-0.6237</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0797</v>
+        <v>-0.5403</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.115</v>
+        <v>0.3501</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3218</v>
+        <v>0.5676</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2068</v>
+        <v>-0.2175</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4288</v>
+        <v>2.4373</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2102</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6518</v>
+        <v>-0.5426</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3357</v>
+        <v>-1.7091</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6839</v>
+        <v>1.1665</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8801</v>
@@ -1156,13 +1156,13 @@
         <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5958</v>
+        <v>0.705</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6849</v>
+        <v>-0.0583</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2808</v>
+        <v>0.7633</v>
       </c>
       <c r="V9" t="n">
         <v>0.2651</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7156</v>
+        <v>-0.5517</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9104</v>
+        <v>0.8292</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.626</v>
+        <v>-1.3809</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3386</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4276</v>
+        <v>0.5916</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6027</v>
+        <v>0.5215</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1751</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9879</v>
+        <v>-1.4897</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2948</v>
+        <v>-2.497</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3069</v>
+        <v>1.0073</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2483</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3822</v>
+        <v>0.8804</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5806</v>
+        <v>0.3784</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8016</v>
+        <v>0.502</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1219</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5827</v>
+        <v>-5.3195</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6742</v>
+        <v>-0.4926</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9085</v>
+        <v>-4.8268</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0459</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2911</v>
+        <v>0.5544</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0522</v>
+        <v>0.1294</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3433</v>
+        <v>0.425</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6559</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6194</v>
+        <v>4.526999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.219299999999998</v>
+        <v>8.1272</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5999</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.393899999999999</v>
+        <v>-9.3939</v>
       </c>
       <c r="H13" t="n">
         <v>-3.321899999999999</v>
@@ -1441,7 +1441,7 @@
         <v>-6.0719</v>
       </c>
       <c r="J13" t="n">
-        <v>4.292299999999999</v>
+        <v>4.292300000000001</v>
       </c>
       <c r="K13" t="n">
         <v>4.287399999999999</v>
@@ -1468,10 +1468,10 @@
         <v>16.604</v>
       </c>
       <c r="S13" t="n">
-        <v>5.9979</v>
+        <v>6.9059</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9866</v>
+        <v>3.8943</v>
       </c>
       <c r="U13" t="n">
         <v>3.0115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5774</v>
+        <v>7.6533</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7612</v>
+        <v>8.5701</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1837</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>6.0786</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3895</v>
+        <v>-0.3137</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3177</v>
+        <v>-0.5088</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0718</v>
+        <v>0.1951</v>
       </c>
       <c r="V14" t="n">
         <v>0.521</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7395</v>
+        <v>6.0453</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1966</v>
+        <v>5.3988</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5429</v>
+        <v>0.6464</v>
       </c>
       <c r="G15" t="n">
         <v>7.0694</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.475</v>
+        <v>-0.1693</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7647</v>
+        <v>-0.5624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2897</v>
+        <v>0.3932</v>
       </c>
       <c r="V15" t="n">
         <v>0.1219</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1861</v>
+        <v>1.9368</v>
       </c>
       <c r="E16" t="n">
-        <v>0.603</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5831</v>
+        <v>1.2327</v>
       </c>
       <c r="G16" t="n">
         <v>3.9458</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0416</v>
+        <v>-0.2909</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5425</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.398</v>
+        <v>0.2516</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1554</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1126</v>
+        <v>0.451</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3594</v>
+        <v>-0.1572</v>
       </c>
       <c r="F17" t="n">
-        <v>0.472</v>
+        <v>0.6081</v>
       </c>
       <c r="G17" t="n">
         <v>1.0023</v>
@@ -1780,13 +1780,13 @@
         <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4209</v>
+        <v>-0.0825</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3631</v>
+        <v>-0.1609</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0578</v>
+        <v>0.0784</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6642</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.207</v>
+        <v>-0.4743</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1816</v>
+        <v>-0.7533</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3886</v>
+        <v>0.2789</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4704</v>
+        <v>-0.4269</v>
       </c>
       <c r="H18" t="n">
-        <v>1.253</v>
+        <v>0.3418</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7827</v>
+        <v>-0.7687</v>
       </c>
       <c r="J18" t="n">
-        <v>0.96</v>
+        <v>-0.5518</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7982</v>
+        <v>0.0819</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1619</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4897</v>
+        <v>0.1249</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4549</v>
+        <v>0.2599</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9445</v>
+        <v>-0.135</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6213</v>
+        <v>-0.8289</v>
       </c>
       <c r="T18" t="n">
-        <v>1.175</v>
+        <v>-0.2015</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5537</v>
+        <v>-0.6274</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4708</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.6894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8192</v>
+        <v>-0.6983</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8544</v>
+        <v>1.0693</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0352</v>
+        <v>-1.7676</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4269</v>
+        <v>0.4704</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3418</v>
+        <v>1.253</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7687</v>
+        <v>-0.7827</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5518</v>
+        <v>0.96</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0819</v>
+        <v>0.7982</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.1619</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1249</v>
+        <v>-0.4897</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2599</v>
+        <v>0.4549</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.135</v>
+        <v>-0.9445</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1737</v>
+        <v>0.13</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3026</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8711</v>
+        <v>0.0673</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.4708</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-3.6894</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9265</v>
+        <v>-2.4528</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4885</v>
+        <v>-3.0952</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6423</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0536</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6983</v>
+        <v>0.172</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4541</v>
+        <v>-0.1526</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2442</v>
+        <v>0.3245</v>
       </c>
       <c r="V20" t="n">
         <v>0.8195</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8872</v>
+        <v>-3.5955</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1094</v>
+        <v>-1.4128</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7778</v>
+        <v>-2.1827</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6585</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1385</v>
+        <v>-0.8467</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0522</v>
+        <v>-0.3555</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0863</v>
+        <v>-0.4912</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8807</v>
+        <v>-3.9901</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2744</v>
+        <v>-1.87</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6063</v>
+        <v>-2.1201</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4469</v>
@@ -2170,13 +2170,13 @@
         <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6059</v>
+        <v>0.2848</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4237</v>
+        <v>-0.0192</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1822</v>
+        <v>0.304</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0466</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5142</v>
+        <v>-5.1241</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0562</v>
+        <v>-4.854</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.458</v>
+        <v>-0.27</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5869</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0725</v>
+        <v>-0.6823</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.773</v>
+        <v>-0.5708</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2995</v>
+        <v>-0.1116</v>
       </c>
       <c r="V23" t="n">
         <v>0.1219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.619199999999999</v>
+        <v>-0.248700000000003</v>
       </c>
       <c r="E24" t="n">
-        <v>3.6001</v>
+        <v>3.599799999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.2192</v>
+        <v>-3.8488</v>
       </c>
       <c r="G24" t="n">
         <v>9.393700000000001</v>
@@ -2326,13 +2326,13 @@
         <v>15.6276</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.998</v>
+        <v>-2.6275</v>
       </c>
       <c r="T24" t="n">
         <v>-3.0115</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.9865</v>
+        <v>0.3839000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-6.0383</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484365_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484365_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,17 +631,22 @@
       </c>
       <c r="X2" t="n">
         <v>-1.3405</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-2.227</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,45 +797,50 @@
       </c>
       <c r="X4" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0274</v>
+        <v>1.7205</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1786</v>
+        <v>0.8717</v>
       </c>
       <c r="F5" t="n">
         <v>0.8488</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.694</v>
+        <v>-2.001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4218</v>
+        <v>1.1149</v>
       </c>
       <c r="I5" t="n">
         <v>-3.1159</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3541</v>
+        <v>0.0472</v>
       </c>
       <c r="K5" t="n">
-        <v>2.255</v>
+        <v>1.9481</v>
       </c>
       <c r="L5" t="n">
         <v>-1.9009</v>
@@ -860,153 +880,163 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2921</v>
+        <v>0.307</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0484</v>
+        <v>0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2437</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9029</v>
+        <v>0.307</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3768</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5261</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4145</v>
+        <v>0.307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8608</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5537</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3174</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2377</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0797</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7429</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3454</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3975</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4288</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2102</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1112</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4445</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5558</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.384</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5188</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6536</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6536</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2091</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09080000000000001</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,636 +1046,677 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4939</v>
+        <v>0.2921</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2026</v>
+        <v>0.0484</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2912</v>
+        <v>0.2437</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6952</v>
+        <v>-0.9029</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2763</v>
+        <v>-0.3768</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4189</v>
+        <v>-0.5261</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5312</v>
+        <v>1.4145</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6526</v>
+        <v>0.8608</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1214</v>
+        <v>0.5537</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1639</v>
+        <v>-2.3174</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6237</v>
+        <v>-1.2377</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5403</v>
+        <v>-1.0797</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3501</v>
+        <v>0.7429</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5676</v>
+        <v>0.3454</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2175</v>
+        <v>0.3975</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4373</v>
+        <v>1.4288</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0.2102</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5426</v>
+        <v>0.1112</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7091</v>
+        <v>-0.4445</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1665</v>
+        <v>0.5558</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8801</v>
+        <v>-0.384</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9112</v>
+        <v>-0.5188</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9688</v>
+        <v>0.1348</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6507</v>
+        <v>-0.6536</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.6536</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.754</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2293</v>
+        <v>0.2696</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0146</v>
+        <v>0.1348</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2148</v>
+        <v>0.1348</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>0.705</v>
+        <v>0.2999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0583</v>
+        <v>0.2091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7633</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2651</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2651</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5517</v>
+        <v>-0.4939</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8292</v>
+        <v>-0.2026</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3809</v>
+        <v>-0.2912</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3386</v>
+        <v>-2.6952</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8102</v>
+        <v>-2.2763</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4716</v>
+        <v>-0.4189</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7652</v>
+        <v>-1.5312</v>
       </c>
       <c r="K10" t="n">
-        <v>0.023</v>
+        <v>-1.6526</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7422</v>
+        <v>0.1214</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1038</v>
+        <v>-1.1639</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.6237</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2706</v>
+        <v>-0.5403</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5916</v>
+        <v>0.3501</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5215</v>
+        <v>0.5676</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.2175</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>2.4373</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4959</v>
+        <v>2.7145</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4897</v>
+        <v>-0.5426</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.497</v>
+        <v>-1.7091</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0073</v>
+        <v>1.1665</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2483</v>
+        <v>-2.8801</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8839</v>
+        <v>-0.9112</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3644</v>
+        <v>-1.9688</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8987</v>
+        <v>-1.6507</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2651</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.754</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3496</v>
+        <v>-1.2293</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6188</v>
+        <v>-0.0146</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2692</v>
+        <v>-1.2148</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8804</v>
+        <v>0.705</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3784</v>
+        <v>-0.0583</v>
       </c>
       <c r="U11" t="n">
-        <v>0.502</v>
+        <v>0.7633</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1219</v>
+        <v>0.2651</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1219</v>
+        <v>0.2651</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3195</v>
+        <v>-0.8587</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4926</v>
+        <v>0.5222</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.8268</v>
+        <v>-1.3809</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0459</v>
+        <v>-0.6456</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4638</v>
+        <v>-1.1172</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4179</v>
+        <v>0.4716</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3314</v>
+        <v>0.4582</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5705</v>
+        <v>-0.284</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9019</v>
+        <v>0.7422</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3773</v>
+        <v>-1.1038</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8933</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.484</v>
+        <v>-0.2706</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5544</v>
+        <v>0.5916</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1294</v>
+        <v>0.5215</v>
       </c>
       <c r="U12" t="n">
-        <v>0.425</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.6559</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.6559</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.526999999999999</v>
+        <v>-1.4897</v>
       </c>
       <c r="E13" t="n">
-        <v>8.1272</v>
+        <v>-2.497</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5999</v>
+        <v>1.0073</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.3939</v>
+        <v>-2.2483</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.321899999999999</v>
+        <v>-1.8839</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0719</v>
+        <v>-0.3644</v>
       </c>
       <c r="J13" t="n">
-        <v>4.292300000000001</v>
+        <v>-1.8987</v>
       </c>
       <c r="K13" t="n">
-        <v>4.287399999999999</v>
+        <v>-1.2651</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005100000000000104</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.686</v>
+        <v>-0.3496</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.6094</v>
+        <v>-0.6188</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.0769</v>
+        <v>0.2692</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9767000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.6272</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>16.604</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>6.9059</v>
+        <v>0.8804</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8943</v>
+        <v>0.3784</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0115</v>
+        <v>0.502</v>
       </c>
       <c r="V13" t="n">
-        <v>6.038200000000001</v>
+        <v>-0.1219</v>
       </c>
       <c r="W13" t="n">
-        <v>15.568</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.529599999999999</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6533</v>
+        <v>-5.3195</v>
       </c>
       <c r="E14" t="n">
-        <v>8.5701</v>
+        <v>-0.4926</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-4.8268</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0786</v>
+        <v>-1.0459</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5437</v>
+        <v>-1.4638</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5349</v>
+        <v>0.4179</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9271</v>
+        <v>1.3314</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2566</v>
+        <v>-0.5705</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6705</v>
+        <v>1.9019</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8485</v>
+        <v>-2.3773</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7129</v>
+        <v>-0.8933</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1356</v>
+        <v>-1.484</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3137</v>
+        <v>0.5544</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5088</v>
+        <v>0.1294</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1951</v>
+        <v>0.425</v>
       </c>
       <c r="V14" t="n">
-        <v>0.521</v>
+        <v>-3.6559</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8028</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0453</v>
+        <v>4.527100000000003</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3988</v>
+        <v>8.1273</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6464</v>
+        <v>-3.5999</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0694</v>
+        <v>-9.3939</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0341</v>
+        <v>-3.321800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0353</v>
+        <v>-6.0719</v>
       </c>
       <c r="J15" t="n">
-        <v>7.923</v>
+        <v>4.292399999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7519</v>
+        <v>4.287500000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1711</v>
+        <v>0.005100000000000104</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8536</v>
+        <v>-13.686</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7178</v>
+        <v>-7.6094</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1358</v>
+        <v>-6.076900000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9767</v>
+        <v>0.9767000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1255</v>
+        <v>-15.6272</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>16.604</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1693</v>
+        <v>6.9059</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5624</v>
+        <v>3.8943</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3932</v>
+        <v>3.0115</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1219</v>
+        <v>6.038200000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1638</v>
+        <v>15.568</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0419</v>
-      </c>
+        <v>-9.5296</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9368</v>
+        <v>7.6533</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7040999999999999</v>
+        <v>8.5701</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2327</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9458</v>
+        <v>6.0786</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7498</v>
+        <v>2.5437</v>
       </c>
       <c r="I16" t="n">
-        <v>3.196</v>
+        <v>3.5349</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1851</v>
+        <v>6.9271</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3929</v>
+        <v>3.2566</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7921</v>
+        <v>3.6705</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2392</v>
+        <v>-0.8485</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6431</v>
+        <v>-0.7129</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4039</v>
+        <v>-0.1356</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1022</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2909</v>
+        <v>-0.3137</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5425</v>
+        <v>-0.5088</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2516</v>
+        <v>0.1951</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1554</v>
+        <v>0.521</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1638</v>
+        <v>3.3238</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3191</v>
+        <v>-2.8028</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.451</v>
+        <v>6.0453</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1572</v>
+        <v>5.3988</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6081</v>
+        <v>0.6464</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0023</v>
+        <v>7.0694</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2203</v>
+        <v>4.0341</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7821</v>
+        <v>3.0353</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6679</v>
+        <v>7.923</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0205</v>
+        <v>4.7519</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6475</v>
+        <v>3.1711</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3344</v>
+        <v>-0.8536</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1998</v>
+        <v>-0.7178</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>-0.1358</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0825</v>
+        <v>-0.1693</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1609</v>
+        <v>-0.5624</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0784</v>
+        <v>0.3932</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6642</v>
+        <v>0.1219</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6642</v>
+        <v>1.1638</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0419</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4743</v>
+        <v>3.3489</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7533</v>
+        <v>3.3489</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2789</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4269</v>
+        <v>3.3489</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3418</v>
+        <v>0.921</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7687</v>
+        <v>2.4279</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5518</v>
+        <v>3.3489</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0819</v>
+        <v>0.921</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>2.4279</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1249</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2599</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.135</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8289</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2015</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6274</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6983</v>
+        <v>1.214</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0693</v>
+        <v>1.214</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7676</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4704</v>
+        <v>1.214</v>
       </c>
       <c r="H19" t="n">
-        <v>1.253</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7827</v>
+        <v>1.214</v>
       </c>
       <c r="J19" t="n">
-        <v>0.96</v>
+        <v>1.214</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7982</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1619</v>
+        <v>1.214</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4897</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4549</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0673</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4708</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6894</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4528</v>
+        <v>0.451</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0952</v>
+        <v>-0.1572</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6423</v>
+        <v>0.6081</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0536</v>
+        <v>1.0023</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5823</v>
+        <v>0.2203</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4714</v>
+        <v>0.7821</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.485</v>
+        <v>0.6679</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2049</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2801</v>
+        <v>0.6475</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5686</v>
+        <v>0.3344</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3773</v>
+        <v>0.1998</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8087</v>
+        <v>0.1346</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.172</v>
+        <v>-0.0825</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1526</v>
+        <v>-0.1609</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3245</v>
+        <v>0.0784</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8195</v>
+        <v>-0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6763</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5955</v>
+        <v>-0.4743</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4128</v>
+        <v>-0.7533</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1827</v>
+        <v>0.2789</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6585</v>
+        <v>-0.4269</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6048</v>
+        <v>0.3418</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0537</v>
+        <v>-0.7687</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2992</v>
+        <v>-0.5518</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2459</v>
+        <v>0.0819</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0533</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3593</v>
+        <v>0.1249</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3589</v>
+        <v>0.2599</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0004</v>
+        <v>-0.135</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8467</v>
+        <v>-0.8289</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3555</v>
+        <v>-0.2015</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4912</v>
+        <v>-0.6274</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2856</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5043</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9901</v>
+        <v>-0.6983</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.87</v>
+        <v>1.0693</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1201</v>
+        <v>-1.7676</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4469</v>
+        <v>0.4704</v>
       </c>
       <c r="H22" t="n">
-        <v>0.012</v>
+        <v>1.253</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4589</v>
+        <v>-0.7827</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1027</v>
+        <v>0.96</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0217</v>
+        <v>0.7982</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>0.1619</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5496</v>
+        <v>-0.4897</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0097</v>
+        <v>0.4549</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5399</v>
+        <v>-0.9445</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2848</v>
+        <v>0.13</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0192</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.304</v>
+        <v>0.0673</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.0466</v>
+        <v>-2.4708</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.0466</v>
+        <v>-3.6894</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1241</v>
+        <v>-1.4121</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.854</v>
+        <v>-2.6448</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.27</v>
+        <v>1.2327</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5869</v>
+        <v>0.5969</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6457</v>
+        <v>-0.1711</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9412</v>
+        <v>0.7681</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7438</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2635</v>
+        <v>0.472</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.4803</v>
+        <v>0.3642</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8431</v>
+        <v>-0.2392</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3822</v>
+        <v>-0.6431</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5391</v>
+        <v>0.4039</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-4.1022</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6823</v>
+        <v>-0.2909</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5708</v>
+        <v>-0.5425</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1116</v>
+        <v>0.2516</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1219</v>
+        <v>-0.1554</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6093</v>
+        <v>1.1638</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4875</v>
+        <v>-1.3191</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,401 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.5955</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.4128</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.1827</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.6585</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.6048</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.0537</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.2992</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.2459</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.0533</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.3593</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3589</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.8467</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.3555</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4912</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2856</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.5043</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. CASTELLO LOGRONO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.6668</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.3091</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6423</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.2676</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.5823</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.6853</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.699</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.2049</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.4941</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.5686</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.3773</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1526</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.6763</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F. VIDAL RAMOS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.9901</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.1201</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.4469</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4589</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.5496</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-3.0466</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-3.0466</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M. CASADO FAJO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.1241</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.854</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.5869</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.6457</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.9412</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.7438</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.2635</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-2.4803</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.8431</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.3822</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.6823</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.5708</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1116</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1219</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.4875</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484365_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-0.248700000000003</v>
       </c>
-      <c r="E24" t="n">
-        <v>3.599799999999997</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E28" t="n">
+        <v>3.599899999999997</v>
+      </c>
+      <c r="F28" t="n">
         <v>-3.8488</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G28" t="n">
         <v>9.393700000000001</v>
       </c>
-      <c r="H24" t="n">
-        <v>3.3219</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6.071700000000002</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="H28" t="n">
+        <v>3.321999999999999</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.0718</v>
+      </c>
+      <c r="J28" t="n">
         <v>13.686</v>
       </c>
-      <c r="K24" t="n">
-        <v>7.609399999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.076700000000001</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="K28" t="n">
+        <v>7.609499999999999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6.076699999999999</v>
+      </c>
+      <c r="M28" t="n">
         <v>-4.2923</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-4.2873</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-0.004899999999999904</v>
       </c>
-      <c r="P24" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="P28" t="n">
+        <v>-0.9767000000000001</v>
+      </c>
+      <c r="Q28" t="n">
         <v>-16.6042</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>15.6276</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>-2.6275</v>
       </c>
-      <c r="T24" t="n">
-        <v>-3.0115</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.3839000000000001</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="T28" t="n">
+        <v>-3.011500000000001</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="V28" t="n">
         <v>-6.0383</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W28" t="n">
         <v>9.529599999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X28" t="n">
         <v>-15.5679</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
